--- a/data/trans_camb/IP07B_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP07B_R-Edad-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -622,645 +631,639 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10,4</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-10,83</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-7,3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,11</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-17,46</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-2,46</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8,62</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>-14,17</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.870383747294102</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>10.39901997869555</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-10.83170301117628</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-7.303214428355398</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>6.112844748161884</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-17.46337061254051</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>-2.455696108149419</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>8.617843275568749</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>-14.16831062042723</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-7,8; 11,97</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2,42; 19,27</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-22,65; 0,27</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-15,88; 1,86</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-1,55; 13,82</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-29,03; -5,94</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-9,45; 3,35</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2,64; 14,38</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-21,88; -5,92</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-7.798620597555206</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>2.421307407552995</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-22.64573751111847</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-15.87644605108089</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-1.554392765041053</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-29.03496757174325</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>-9.44591445903078</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>2.639223788536649</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>-21.87944437815761</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15,03%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-15,65%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-9,15%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-21,87%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-3,31%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>11,61%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>-19,09%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.97032434518245</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>19.27485802312691</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.2723745374713348</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1.863075803501637</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>13.82259889917483</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>-5.93975477917538</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>3.349600173895686</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>14.38410426658944</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>-5.923343266289077</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-10,53; 19,14</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3,29; 30,47</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-30,82; 0,74</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-18,98; 2,45</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-1,79; 18,67</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-35,6; -8,11</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-12,23; 4,72</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3,42; 20,36</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>-28,46; -8,35</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0.02702904149287655</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.1502769380326621</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.1565296696740189</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.09148016378733978</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.07656957689716298</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2187464190715228</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.03308080305130327</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.1160913906162944</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>-0.1908620092073393</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-5,61</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5,97</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-17,34</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-5,58</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,15</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-5,55</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-5,57</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>6,08</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>-12,15</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>-0.105313755043619</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.03291124021475565</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.3082036806447475</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.1897818822910239</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.01787564311390336</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3559687536265258</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1223253555525772</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>0.03422899130228021</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>-0.284558085909282</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-13,32; 1,77</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,92; 13,09</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-29,86; -7,69</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-13,5; 2,29</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-0,32; 13,76</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-14,7; 2,67</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-11,52; -0,09</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,92; 10,62</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>-19,91; -5,28</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0.1914148322024078</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.3046986070326461</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.007403472575787463</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.0244502625603337</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1866986566819659</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.08106971795791869</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.04716842694766863</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.2036451138037745</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>-0.08352788348163388</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-7,09%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-21,95%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-7,35%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,09%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-7,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-7,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>-15,68%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-5.605745368861637</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>5.973828670971715</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-17.34403598329244</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-5.578305655471338</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>6.145103946040608</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-5.54526040111879</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>-5.567325669436263</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>6.077495545582535</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>-12.15183751975437</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-16,02; 2,16</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,0; 17,44</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-36,87; -9,98</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-17,03; 3,29</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-0,41; 19,24</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-18,78; 3,45</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-14,59; -0,16</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1,17; 14,01</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>-25,6; -7,48</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-13.31561938348437</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.916930754936358</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-29.85980849838766</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-13.50348049114128</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.3207893884178722</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-14.70317095003427</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>-11.51999474416833</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0.9193872978478812</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>-19.91297146378743</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-2,79</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>7,19</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-14,62</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-6,04</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,7</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-9,97</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-4,36</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>6,98</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>-12,79</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.772030521801936</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>13.09035645579771</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-7.688079509021284</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.29333445311305</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>13.75557370442301</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>2.673097623048005</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>-0.08659418129109281</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>10.62450509030245</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>-5.275789229791044</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-8,33; 2,84</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1,52; 12,58</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-22,9; -6,57</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-11,73; -0,39</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,61; 11,89</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-16,88; -3,33</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-8,44; 0,26</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3,23; 11,06</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-18,17; -7,81</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>-0.07093423423721971</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.07559190336998443</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.2194687468131412</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.07346765058270603</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.08093252277406317</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.07303243649618346</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.0718295659923346</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.07841177133863336</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>-0.1567828553384606</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-3,71%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>9,58%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-19,46%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-7,8%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8,66%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-12,88%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-5,72%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>-16,79%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-0.1602149785418329</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.01004775430582834</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.3687447504939546</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.1703108275607584</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.004098231584686522</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.187840482969093</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1459141941323786</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>0.01169582437746328</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>-0.2560434734479892</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-10,64; 3,97</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>1,95; 17,37</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-29,96; -9,25</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-14,71; -0,54</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>2,04; 15,98</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-21,46; -4,48</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-10,87; 0,32</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>4,19; 15,04</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>-23,57; -10,55</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>0.02162237263462023</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.1743885897090257</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-0.09976047586409223</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.03287915983944645</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1923510884040026</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.03449688090222715</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>-0.001611232878175134</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.140101091770595</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>-0.07477120012216326</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>-2.78822760933064</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>7.19151034670118</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-14.61541005623015</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-6.037731470271823</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>6.703574220500452</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-9.972497442724727</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>-4.359993955869134</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>6.982781085907508</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>-12.79467980761135</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-8.333227954056802</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1.524421956047609</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-22.90489755886076</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-11.72808342809744</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>1.608064549638663</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-16.87768529497152</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>-8.440367423983005</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>3.232945755415159</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>-18.16527910149426</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.838258905428419</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>12.58433615704038</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-6.572642298293192</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-0.394158255361426</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>11.89007996420477</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>-3.33456795085831</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>0.2551784950078739</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>11.0616731246883</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>-7.814814798427122</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>-0.03713019126514712</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.09576770338430238</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.1946300829209053</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.07797868643974518</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.08657819824213381</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.1287970912479786</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-0.05720067301779938</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.09161016774167703</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>-0.1678590161936876</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>-0.1064162478384696</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0.01953715071758119</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.2995710569645069</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.1470987955442948</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0.0203862139144756</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.2146208483255523</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.1087431837420003</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>0.04185273122417576</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>-0.2357432491371567</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>0.03973637793985644</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.173740458616592</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>-0.09252927583010338</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>-0.005371166063493356</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.1597967085504677</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>-0.04477379972862754</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.003184468929475491</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.1504231843845173</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>-0.105524017333222</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1268,12 +1271,12 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A12:A15"/>
     <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
